--- a/output/pdf_financials_xlsx/IN.xlsx
+++ b/output/pdf_financials_xlsx/IN.xlsx
@@ -3046,25 +3046,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.057114</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.057114</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.845097</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.103002</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.130619</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.134119</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.190288</v>
       </c>
     </row>
     <row r="93">
@@ -4896,7 +4896,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -5427,7 +5431,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -5635,7 +5643,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.057114</v>
       </c>
@@ -5898,7 +5910,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.057114</v>
       </c>

--- a/output/pdf_financials_xlsx/IN.xlsx
+++ b/output/pdf_financials_xlsx/IN.xlsx
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.01929</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>-0.150142</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.150142</v>
+        <v>-0.169432</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.816326</v>
@@ -1242,7 +1242,7 @@
         <v>-0.150142</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.150142</v>
+        <v>-0.169432</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.816326</v>
@@ -1386,25 +1386,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.342473</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017187</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.895329</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.663998</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.560535</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.174363</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.025175</v>
       </c>
     </row>
     <row r="35">
@@ -1442,25 +1442,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.342473</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017187</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.895329</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.663998</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.560535</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.174363</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.025175</v>
       </c>
     </row>
     <row r="37">
@@ -1784,19 +1784,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.915464</v>
+        <v>0.020135</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.674083</v>
+        <v>0.010085</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.559711</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.199049</v>
+        <v>0.024686</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.028147</v>
+        <v>0.002972</v>
       </c>
     </row>
     <row r="49">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4569,7 +4569,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -12466,7 +12470,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">

--- a/output/pdf_financials_xlsx/IN.xlsx
+++ b/output/pdf_financials_xlsx/IN.xlsx
@@ -3283,10 +3283,10 @@
         <v>-0.001893</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.058135</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01401</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0.053799</v>
@@ -7347,7 +7347,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -7902,7 +7906,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
